--- a/data/BF2_MASTERFILE_Formatted.xlsx
+++ b/data/BF2_MASTERFILE_Formatted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ec16df870fa087b/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="8_{E79E8174-D479-4683-A4E2-9332D1E22489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03DE348E-C4D3-4F36-AE82-94D6615FABBC}"/>
+  <xr:revisionPtr revIDLastSave="393" documentId="8_{E79E8174-D479-4683-A4E2-9332D1E22489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BAC8CFA-F298-4F43-ABCA-DA69B6407220}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="136">
   <si>
     <t>JINDAL STEEL LIMITED</t>
   </si>
@@ -440,6 +440,9 @@
   <si>
     <t>Top Pressure (bar)</t>
   </si>
+  <si>
+    <t>July</t>
+  </si>
 </sst>
 </file>
 
@@ -739,7 +742,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -863,6 +866,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3720,7 +3726,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:AE62"/>
+  <dimension ref="A1:AE63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" style="22" bestFit="1" customWidth="1"/>
@@ -3747,7 +3753,8 @@
     <col min="28" max="28" width="22" style="8" customWidth="1"/>
     <col min="29" max="30" width="13" style="8" customWidth="1"/>
     <col min="31" max="31" width="40" style="8" customWidth="1"/>
-    <col min="32" max="16384" width="8.7265625" style="8"/>
+    <col min="32" max="32" width="26" style="8" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="8.7265625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -9696,6 +9703,101 @@
         <v>63</v>
       </c>
       <c r="AE62" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="56">
+        <v>46218</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C63" s="18">
+        <v>6250</v>
+      </c>
+      <c r="D63" s="18">
+        <v>6185</v>
+      </c>
+      <c r="E63" s="18">
+        <v>2.38</v>
+      </c>
+      <c r="F63" s="18">
+        <v>6100</v>
+      </c>
+      <c r="G63" s="18">
+        <v>1185</v>
+      </c>
+      <c r="H63" s="18">
+        <v>3.35</v>
+      </c>
+      <c r="I63" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="J63" s="18">
+        <v>198</v>
+      </c>
+      <c r="K63" s="18">
+        <v>1750</v>
+      </c>
+      <c r="L63" s="18">
+        <v>4200</v>
+      </c>
+      <c r="M63" s="18">
+        <v>1050</v>
+      </c>
+      <c r="N63" s="18">
+        <v>1985</v>
+      </c>
+      <c r="O63" s="18">
+        <v>145</v>
+      </c>
+      <c r="P63" s="18">
+        <v>265</v>
+      </c>
+      <c r="Q63" s="18">
+        <v>321</v>
+      </c>
+      <c r="R63" s="18">
+        <v>23</v>
+      </c>
+      <c r="S63" s="18">
+        <v>344</v>
+      </c>
+      <c r="T63" s="18">
+        <v>60.5</v>
+      </c>
+      <c r="U63" s="18">
+        <v>15.1</v>
+      </c>
+      <c r="V63" s="18">
+        <v>57.8</v>
+      </c>
+      <c r="W63" s="18">
+        <v>3.52</v>
+      </c>
+      <c r="X63" s="18">
+        <v>285</v>
+      </c>
+      <c r="Y63" s="18">
+        <v>1762.7</v>
+      </c>
+      <c r="Z63" s="18">
+        <v>100</v>
+      </c>
+      <c r="AA63" s="18">
+        <v>97.8</v>
+      </c>
+      <c r="AB63" s="18">
+        <v>99.2</v>
+      </c>
+      <c r="AC63" s="18">
+        <v>97</v>
+      </c>
+      <c r="AD63" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE63" s="18" t="s">
         <v>64</v>
       </c>
     </row>

--- a/data/BF2_MASTERFILE_Formatted.xlsx
+++ b/data/BF2_MASTERFILE_Formatted.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="393" documentId="8_{E79E8174-D479-4683-A4E2-9332D1E22489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BAC8CFA-F298-4F43-ABCA-DA69B6407220}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="672" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BF-2_Subhadrika" sheetId="1" r:id="rId1"/>
@@ -852,6 +852,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -866,9 +869,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3476,49 +3476,49 @@
     </row>
     <row r="2" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="6" spans="1:8" ht="20" x14ac:dyDescent="0.4">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
     </row>
     <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
@@ -3529,85 +3529,85 @@
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="52"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="52"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="52"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="52"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="52"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="52"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="52"/>
     </row>
     <row r="19" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
@@ -3667,37 +3667,37 @@
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="52"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="52"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -9707,7 +9707,7 @@
       </c>
     </row>
     <row r="63" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="56">
+      <c r="A63" s="47">
         <v>46218</v>
       </c>
       <c r="B63" s="18" t="s">

--- a/data/BF2_MASTERFILE_Formatted.xlsx
+++ b/data/BF2_MASTERFILE_Formatted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ec16df870fa087b/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="393" documentId="8_{E79E8174-D479-4683-A4E2-9332D1E22489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BAC8CFA-F298-4F43-ABCA-DA69B6407220}"/>
+  <xr:revisionPtr revIDLastSave="417" documentId="8_{E79E8174-D479-4683-A4E2-9332D1E22489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B8862D0-A991-4F2F-8389-844EE94A157F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="672" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BF-2_Subhadrika" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="136">
   <si>
     <t>JINDAL STEEL LIMITED</t>
   </si>
@@ -441,13 +441,16 @@
     <t>Top Pressure (bar)</t>
   </si>
   <si>
-    <t>July</t>
+    <t>June</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0"/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -742,7 +745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -852,9 +855,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -870,6 +870,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1528,415 +1534,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2797,6 +2394,415 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3049,67 +3055,67 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tbl_Process_Parameters" displayName="Tbl_Process_Parameters" ref="A1:AE62" headerRowDxfId="98" totalsRowDxfId="97">
-  <autoFilter ref="A1:AE62" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tbl_Process_Parameters" displayName="Tbl_Process_Parameters" ref="A1:AE63" headerRowDxfId="78" totalsRowDxfId="77">
+  <autoFilter ref="A1:AE63" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hot metal to SMS" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Production" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Productivity" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Wind Volume" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="HBT" dataDxfId="90"/>
-    <tableColumn id="34" xr3:uid="{CF5B08E0-C9B6-4D76-8810-2DFC7863B7CB}" name="Hot Blast Pressure (bar)" dataDxfId="89"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="O2 Enrichment (%)" dataDxfId="88"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Oxygen Consumption" dataDxfId="87"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Iron Ore" dataDxfId="86"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Sinter Used" dataDxfId="85"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Pellet Used" dataDxfId="84"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Coke Used" dataDxfId="83"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PCI Used" dataDxfId="82"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Limestone" dataDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Coke Rate" dataDxfId="80"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="PCI Coal Rate" dataDxfId="79">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hot metal to SMS" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Production" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Productivity" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Wind Volume" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="HBT" dataDxfId="70"/>
+    <tableColumn id="34" xr3:uid="{CF5B08E0-C9B6-4D76-8810-2DFC7863B7CB}" name="Hot Blast Pressure (bar)" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="O2 Enrichment (%)" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Oxygen Consumption" dataDxfId="67"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Iron Ore" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Sinter Used" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Pellet Used" dataDxfId="64"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Coke Used" dataDxfId="63"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PCI Used" dataDxfId="62"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Limestone" dataDxfId="61"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Coke Rate" dataDxfId="60"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="PCI Coal Rate" dataDxfId="59">
       <calculatedColumnFormula>S2-Q2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Total Fuel Rate" dataDxfId="78"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Sinter Percent" dataDxfId="77"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Pellet Percent" dataDxfId="76"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Iron in Burden" dataDxfId="75"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Ore/Coke" dataDxfId="74"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Slag Rate" dataDxfId="73"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="total slag generation" dataDxfId="72"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Furnace Availability" dataDxfId="71"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Performance Rate" dataDxfId="70"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Quality product rate" dataDxfId="69"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="O E E" dataDxfId="68"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Status" dataDxfId="67"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Comment" dataDxfId="66"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Total Fuel Rate" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Sinter Percent" dataDxfId="57"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Pellet Percent" dataDxfId="56"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Iron in Burden" dataDxfId="55"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Ore/Coke" dataDxfId="54"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Slag Rate" dataDxfId="53"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="total slag generation" dataDxfId="52"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Furnace Availability" dataDxfId="51"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Performance Rate" dataDxfId="50"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Quality product rate" dataDxfId="49"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="O E E" dataDxfId="48"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Status" dataDxfId="47"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Comment" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tbl_Raw_Material_Analysis" displayName="Tbl_Raw_Material_Analysis" ref="A1:P62" headerRowDxfId="65" totalsRowDxfId="64">
-  <autoFilter ref="A1:P62" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tbl_Raw_Material_Analysis" displayName="Tbl_Raw_Material_Analysis" ref="A1:P63" headerRowDxfId="98" totalsRowDxfId="97">
+  <autoFilter ref="A1:P63" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Al%(sinter)" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Fe total%(sinter)" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="FeO%(sinter)" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Basicity(sinter)" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MPS(sinter)" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Al%(pellet)" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="CaO%(pellet)" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="MgO%(pellet)" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CCS(pellet)" dataDxfId="54"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VM%(coke)" dataDxfId="53"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Ash%(coke)" dataDxfId="52"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Moisture%(coke)" dataDxfId="51"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="MPS(coke)" dataDxfId="50"/>
-    <tableColumn id="15" xr3:uid="{07F0C67E-598C-49B2-B37D-70A5A9C5B14D}" name="M10(coke)" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="16" xr3:uid="{7290EAF3-FA1C-47B8-87F0-5CF9AFED67CA}" name="M40(coke)" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Al%(sinter)" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Fe total%(sinter)" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="FeO%(sinter)" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Basicity(sinter)" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MPS(sinter)" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Al%(pellet)" dataDxfId="90"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="CaO%(pellet)" dataDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="MgO%(pellet)" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CCS(pellet)" dataDxfId="87"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VM%(coke)" dataDxfId="86"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Ash%(coke)" dataDxfId="85"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Moisture%(coke)" dataDxfId="84"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="MPS(coke)" dataDxfId="83"/>
+    <tableColumn id="15" xr3:uid="{07F0C67E-598C-49B2-B37D-70A5A9C5B14D}" name="M10(coke)" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="16" xr3:uid="{7290EAF3-FA1C-47B8-87F0-5CF9AFED67CA}" name="M40(coke)" dataDxfId="80" totalsRowDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3476,49 +3482,49 @@
     </row>
     <row r="2" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
+      <c r="B2" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
     </row>
     <row r="3" spans="1:8" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
     </row>
     <row r="6" spans="1:8" ht="20" x14ac:dyDescent="0.4">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
     </row>
     <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
@@ -3529,85 +3535,85 @@
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="52"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="52"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="52"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="52"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="51"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="52"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="52"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="51"/>
     </row>
     <row r="19" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
@@ -3667,37 +3673,37 @@
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="D27" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="52"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="51"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="50" t="s">
+      <c r="D28" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="52"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="51"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="50" t="s">
+      <c r="D29" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="52"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -9707,99 +9713,36 @@
       </c>
     </row>
     <row r="63" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="47">
-        <v>46218</v>
+      <c r="A63" s="16">
+        <v>46174</v>
       </c>
       <c r="B63" s="18" t="s">
         <v>135</v>
       </c>
       <c r="C63" s="18">
-        <v>6250</v>
+        <v>10000</v>
       </c>
       <c r="D63" s="18">
-        <v>6185</v>
-      </c>
-      <c r="E63" s="18">
-        <v>2.38</v>
+        <v>8784</v>
+      </c>
+      <c r="E63" s="57">
+        <f>Tbl_Process_Parameters[[#This Row],[Production]]/4636</f>
+        <v>1.8947368421052631</v>
       </c>
       <c r="F63" s="18">
-        <v>6100</v>
+        <v>7666</v>
       </c>
       <c r="G63" s="18">
-        <v>1185</v>
-      </c>
-      <c r="H63" s="18">
-        <v>3.35</v>
-      </c>
-      <c r="I63" s="18">
-        <v>3.2</v>
-      </c>
-      <c r="J63" s="18">
-        <v>198</v>
-      </c>
-      <c r="K63" s="18">
-        <v>1750</v>
-      </c>
-      <c r="L63" s="18">
-        <v>4200</v>
-      </c>
-      <c r="M63" s="18">
-        <v>1050</v>
-      </c>
-      <c r="N63" s="18">
-        <v>1985</v>
-      </c>
-      <c r="O63" s="18">
-        <v>145</v>
-      </c>
-      <c r="P63" s="18">
-        <v>265</v>
-      </c>
-      <c r="Q63" s="18">
-        <v>321</v>
-      </c>
-      <c r="R63" s="18">
-        <v>23</v>
-      </c>
-      <c r="S63" s="18">
-        <v>344</v>
-      </c>
-      <c r="T63" s="18">
-        <v>60.5</v>
-      </c>
-      <c r="U63" s="18">
-        <v>15.1</v>
-      </c>
-      <c r="V63" s="18">
-        <v>57.8</v>
-      </c>
-      <c r="W63" s="18">
-        <v>3.52</v>
-      </c>
-      <c r="X63" s="18">
-        <v>285</v>
-      </c>
-      <c r="Y63" s="18">
-        <v>1762.7</v>
-      </c>
-      <c r="Z63" s="18">
-        <v>100</v>
-      </c>
-      <c r="AA63" s="18">
-        <v>97.8</v>
-      </c>
-      <c r="AB63" s="18">
-        <v>99.2</v>
-      </c>
-      <c r="AC63" s="18">
-        <v>97</v>
-      </c>
-      <c r="AD63" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE63" s="18" t="s">
-        <v>64</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="H63" s="9">
+        <v>6.6</v>
+      </c>
+      <c r="R63" s="46">
+        <f>S63-Q63</f>
+        <v>0</v>
+      </c>
+      <c r="AE63" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -9815,7 +9758,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" style="8" customWidth="1"/>
@@ -12894,6 +12837,15 @@
       <c r="P62" s="39">
         <v>87.68</v>
       </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A63" s="16">
+        <v>46174</v>
+      </c>
+      <c r="B63" s="12">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="N63" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/BF2_MASTERFILE_Formatted.xlsx
+++ b/data/BF2_MASTERFILE_Formatted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ec16df870fa087b/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="417" documentId="8_{E79E8174-D479-4683-A4E2-9332D1E22489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B8862D0-A991-4F2F-8389-844EE94A157F}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="8_{E79E8174-D479-4683-A4E2-9332D1E22489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB446DDC-0C09-45F3-8790-CF64DAF0912A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="672" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="136">
   <si>
     <t>JINDAL STEEL LIMITED</t>
   </si>
@@ -449,7 +449,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -745,7 +745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -855,6 +855,12 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -870,12 +876,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1534,6 +1535,415 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2394,415 +2804,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -3055,67 +3056,67 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tbl_Process_Parameters" displayName="Tbl_Process_Parameters" ref="A1:AE63" headerRowDxfId="78" totalsRowDxfId="77">
-  <autoFilter ref="A1:AE63" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tbl_Process_Parameters" displayName="Tbl_Process_Parameters" ref="A1:AE64" headerRowDxfId="98" totalsRowDxfId="97">
+  <autoFilter ref="A1:AE64" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month" dataDxfId="75"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hot metal to SMS" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Production" dataDxfId="73"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Productivity" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Wind Volume" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="HBT" dataDxfId="70"/>
-    <tableColumn id="34" xr3:uid="{CF5B08E0-C9B6-4D76-8810-2DFC7863B7CB}" name="Hot Blast Pressure (bar)" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="O2 Enrichment (%)" dataDxfId="68"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Oxygen Consumption" dataDxfId="67"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Iron Ore" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Sinter Used" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Pellet Used" dataDxfId="64"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Coke Used" dataDxfId="63"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PCI Used" dataDxfId="62"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Limestone" dataDxfId="61"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Coke Rate" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="PCI Coal Rate" dataDxfId="59">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Month" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Hot metal to SMS" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Production" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Productivity" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Wind Volume" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="HBT" dataDxfId="90"/>
+    <tableColumn id="34" xr3:uid="{CF5B08E0-C9B6-4D76-8810-2DFC7863B7CB}" name="Hot Blast Pressure (bar)" dataDxfId="89"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="O2 Enrichment (%)" dataDxfId="88"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Oxygen Consumption" dataDxfId="87"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Iron Ore" dataDxfId="86"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Sinter Used" dataDxfId="85"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Pellet Used" dataDxfId="84"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Coke Used" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="PCI Used" dataDxfId="82"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Limestone" dataDxfId="81"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Coke Rate" dataDxfId="80"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="PCI Coal Rate" dataDxfId="79">
       <calculatedColumnFormula>S2-Q2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Total Fuel Rate" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Sinter Percent" dataDxfId="57"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Pellet Percent" dataDxfId="56"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Iron in Burden" dataDxfId="55"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Ore/Coke" dataDxfId="54"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Slag Rate" dataDxfId="53"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="total slag generation" dataDxfId="52"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Furnace Availability" dataDxfId="51"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Performance Rate" dataDxfId="50"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Quality product rate" dataDxfId="49"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="O E E" dataDxfId="48"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Status" dataDxfId="47"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Comment" dataDxfId="46"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Total Fuel Rate" dataDxfId="78"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Sinter Percent" dataDxfId="77"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Pellet Percent" dataDxfId="76"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Iron in Burden" dataDxfId="75"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Ore/Coke" dataDxfId="74"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Slag Rate" dataDxfId="73"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="total slag generation" dataDxfId="72"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Furnace Availability" dataDxfId="71"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Performance Rate" dataDxfId="70"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Quality product rate" dataDxfId="69"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="O E E" dataDxfId="68"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Status" dataDxfId="67"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Comment" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tbl_Raw_Material_Analysis" displayName="Tbl_Raw_Material_Analysis" ref="A1:P63" headerRowDxfId="98" totalsRowDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tbl_Raw_Material_Analysis" displayName="Tbl_Raw_Material_Analysis" ref="A1:P63" headerRowDxfId="65" totalsRowDxfId="64">
   <autoFilter ref="A1:P63" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Al%(sinter)" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Fe total%(sinter)" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="FeO%(sinter)" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Basicity(sinter)" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MPS(sinter)" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Al%(pellet)" dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="CaO%(pellet)" dataDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="MgO%(pellet)" dataDxfId="88"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CCS(pellet)" dataDxfId="87"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VM%(coke)" dataDxfId="86"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Ash%(coke)" dataDxfId="85"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Moisture%(coke)" dataDxfId="84"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="MPS(coke)" dataDxfId="83"/>
-    <tableColumn id="15" xr3:uid="{07F0C67E-598C-49B2-B37D-70A5A9C5B14D}" name="M10(coke)" dataDxfId="82" totalsRowDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{7290EAF3-FA1C-47B8-87F0-5CF9AFED67CA}" name="M40(coke)" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Date" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Al%(sinter)" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Fe total%(sinter)" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="FeO%(sinter)" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Basicity(sinter)" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MPS(sinter)" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Al%(pellet)" dataDxfId="57"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="CaO%(pellet)" dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="MgO%(pellet)" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="CCS(pellet)" dataDxfId="54"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VM%(coke)" dataDxfId="53"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Ash%(coke)" dataDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Moisture%(coke)" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="MPS(coke)" dataDxfId="50"/>
+    <tableColumn id="15" xr3:uid="{07F0C67E-598C-49B2-B37D-70A5A9C5B14D}" name="M10(coke)" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="16" xr3:uid="{7290EAF3-FA1C-47B8-87F0-5CF9AFED67CA}" name="M40(coke)" dataDxfId="47" totalsRowDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3482,49 +3483,49 @@
     </row>
     <row r="2" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="3" spans="1:8" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="6" spans="1:8" ht="20" x14ac:dyDescent="0.4">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
     </row>
     <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
@@ -3535,85 +3536,85 @@
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="53"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="53"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="53"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="53"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="53"/>
     </row>
     <row r="19" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
@@ -3673,37 +3674,37 @@
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="49" t="s">
+      <c r="D27" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="53"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="51"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="53"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3732,7 +3733,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:AE63"/>
+  <dimension ref="A1:AE64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" style="22" bestFit="1" customWidth="1"/>
@@ -9725,7 +9726,7 @@
       <c r="D63" s="18">
         <v>8784</v>
       </c>
-      <c r="E63" s="57">
+      <c r="E63" s="48">
         <f>Tbl_Process_Parameters[[#This Row],[Production]]/4636</f>
         <v>1.8947368421052631</v>
       </c>
@@ -9742,7 +9743,35 @@
         <f>S63-Q63</f>
         <v>0</v>
       </c>
-      <c r="AE63" s="56"/>
+      <c r="AE63" s="47"/>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A64" s="16">
+        <v>46175</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="8">
+        <v>20000</v>
+      </c>
+      <c r="D64" s="8">
+        <v>7111</v>
+      </c>
+      <c r="E64" s="48">
+        <f>Tbl_Process_Parameters[[#This Row],[Production]]/4636</f>
+        <v>1.5338654012079378</v>
+      </c>
+      <c r="F64" s="8">
+        <v>8878</v>
+      </c>
+      <c r="H64" s="9"/>
+      <c r="Q64" s="18"/>
+      <c r="R64" s="58">
+        <f>S64-Q64</f>
+        <v>0</v>
+      </c>
+      <c r="AE64" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
